--- a/Test Execution Report_Git/Feature Reports/Addnewuser.xlsx
+++ b/Test Execution Report_Git/Feature Reports/Addnewuser.xlsx
@@ -500,7 +500,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K2" t="str">
-        <v>Error: expect(locator).toBeVisible() failed Locator: locator('text=7 Pending Actions') Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for locator('text=7 Pending Actions')</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L2" t="str">
         <v>FAIL</v>
@@ -509,13 +509,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N2" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O2" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P2" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="3">
@@ -550,22 +550,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K3" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L3" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M3" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N3" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O3" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="4">
@@ -600,22 +600,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K4" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L4" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M4" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N4" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O4" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P4" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="5">
@@ -650,7 +650,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K5" t="str">
-        <v>Error: expect(received).toBeGreaterThanOrEqual(expected) Expected: &gt;= 1 Received: 0</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L5" t="str">
         <v>FAIL</v>
@@ -659,13 +659,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N5" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O5" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P5" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="6">
@@ -700,22 +700,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K6" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L6" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M6" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N6" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O6" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="7">
@@ -750,22 +750,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K7" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L7" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M7" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N7" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O7" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="8">
@@ -800,22 +800,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K8" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L8" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M8" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N8" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O8" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="9">
@@ -859,13 +859,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N9" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O9" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P9" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="10">
@@ -900,22 +900,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K10" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
       </c>
       <c r="L10" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M10" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N10" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O10" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="11">
@@ -950,22 +950,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K11" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L11" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M11" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N11" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O11" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P11" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="12">
@@ -1009,13 +1009,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N12" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O12" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P12" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="13">
@@ -1050,22 +1050,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K13" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L13" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M13" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N13" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O13" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P13" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="14">
@@ -1100,22 +1100,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K14" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L14" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M14" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N14" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O14" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P14" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="15">
@@ -1150,22 +1150,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K15" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L15" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M15" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N15" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O15" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P15" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="16">
@@ -1200,22 +1200,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K16" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L16" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M16" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N16" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O16" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P16" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="17">
@@ -1250,22 +1250,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K17" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L17" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M17" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N17" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O17" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P17" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="18">
@@ -1300,7 +1300,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K18" t="str">
-        <v>Error: expect(received).toBeTruthy() Received: false</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L18" t="str">
         <v>FAIL</v>
@@ -1309,13 +1309,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N18" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O18" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P18" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="19">
@@ -1350,22 +1350,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K19" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L19" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M19" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N19" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O19" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P19" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="20">
@@ -1400,22 +1400,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K20" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L20" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M20" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N20" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O20" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P20" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="21">
@@ -1450,22 +1450,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K21" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L21" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M21" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N21" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O21" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P21" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="22">
@@ -1500,22 +1500,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K22" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L22" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M22" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N22" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O22" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="23">
@@ -1550,22 +1550,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K23" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L23" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M23" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N23" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O23" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P23" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="24">
@@ -1600,22 +1600,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K24" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L24" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M24" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N24" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O24" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P24" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="25">
@@ -1650,22 +1650,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K25" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L25" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M25" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N25" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O25" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P25" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="26">
@@ -1700,22 +1700,22 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K26" t="str">
-        <v>All assertions passed via Playwright</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L26" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="M26" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N26" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O26" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P26" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="27">
@@ -1750,7 +1750,7 @@
         <v>Test assertions pass per spec definition</v>
       </c>
       <c r="K27" t="str">
-        <v>Error: expect(received).not.toMatch(expected) Expected pattern: not /ActionQueueDetails/ Received string: "http://customerportal.dev-ts.online/Ticket/ActionQueueDetails/1345"</v>
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
       </c>
       <c r="L27" t="str">
         <v>FAIL</v>
@@ -1759,13 +1759,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N27" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O27" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P27" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="28" xml:space="preserve">
@@ -1814,13 +1814,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N28" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O28" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P28" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="29" xml:space="preserve">
@@ -1860,22 +1860,22 @@
         <v>'Success — Operation completed successfully.' shown; form resets; Partner Admin user created</v>
       </c>
       <c r="K29" t="str">
-        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+        <v>All assertions passed via Playwright</v>
       </c>
       <c r="L29" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="M29" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N29" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O29" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P29" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="30" xml:space="preserve">
@@ -1923,13 +1923,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N30" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O30" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P30" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="31" xml:space="preserve">
@@ -1969,22 +1969,22 @@
         <v>Password input visible when Manual selected; user created successfully</v>
       </c>
       <c r="K31" t="str">
-        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+        <v>All assertions passed via Playwright</v>
       </c>
       <c r="L31" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="M31" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N31" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O31" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P31" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="32" xml:space="preserve">
@@ -2022,22 +2022,22 @@
         <v>User created with Inactive status; success feedback shown</v>
       </c>
       <c r="K32" t="str">
-        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+        <v>All assertions passed via Playwright</v>
       </c>
       <c r="L32" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="M32" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N32" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O32" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P32" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="33" xml:space="preserve">
@@ -2084,13 +2084,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N33" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O33" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P33" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="34" xml:space="preserve">
@@ -2137,13 +2137,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N34" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O34" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P34" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="35" xml:space="preserve">
@@ -2181,22 +2181,22 @@
         <v>1-char First Name accepted; user created successfully</v>
       </c>
       <c r="K35" t="str">
-        <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
+        <v>All assertions passed via Playwright</v>
       </c>
       <c r="L35" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="M35" t="str">
         <v>Playwright Automation</v>
       </c>
       <c r="N35" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O35" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P35" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="36" xml:space="preserve">
@@ -2242,13 +2242,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N36" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O36" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P36" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="37" xml:space="preserve">
@@ -2294,13 +2294,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N37" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O37" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P37" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="38" xml:space="preserve">
@@ -2347,13 +2347,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N38" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O38" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P38" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="39" xml:space="preserve">
@@ -2401,13 +2401,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N39" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O39" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P39" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="40" xml:space="preserve">
@@ -2457,13 +2457,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N40" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O40" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P40" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="41" xml:space="preserve">
@@ -2509,13 +2509,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N41" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O41" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P41" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="42" xml:space="preserve">
@@ -2564,13 +2564,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N42" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O42" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P42" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="43">
@@ -2614,13 +2614,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N43" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O43" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P43" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="44">
@@ -2664,13 +2664,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N44" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O44" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P44" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="45">
@@ -2714,13 +2714,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N45" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O45" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P45" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="46">
@@ -2764,13 +2764,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N46" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O46" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P46" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="47">
@@ -2814,13 +2814,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N47" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O47" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P47" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="48">
@@ -2864,13 +2864,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N48" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O48" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P48" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="49">
@@ -2914,13 +2914,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N49" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O49" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P49" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="50">
@@ -2964,13 +2964,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N50" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O50" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P50" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="51">
@@ -3014,13 +3014,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N51" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O51" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P51" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="52">
@@ -3064,13 +3064,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N52" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O52" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P52" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="53">
@@ -3114,13 +3114,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N53" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O53" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P53" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="54">
@@ -3164,13 +3164,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N54" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O54" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P54" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="55">
@@ -3214,13 +3214,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N55" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O55" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P55" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="56">
@@ -3264,13 +3264,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N56" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O56" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P56" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="57">
@@ -3314,13 +3314,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N57" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O57" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P57" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="58">
@@ -3364,13 +3364,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N58" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O58" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P58" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="59">
@@ -3414,13 +3414,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N59" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O59" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P59" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="60">
@@ -3464,13 +3464,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N60" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O60" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P60" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="61">
@@ -3514,13 +3514,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N61" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O61" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P61" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="62">
@@ -3564,13 +3564,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N62" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O62" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P62" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="63">
@@ -3614,13 +3614,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N63" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O63" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P63" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="64">
@@ -3664,13 +3664,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N64" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O64" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P64" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="65">
@@ -3714,13 +3714,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N65" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O65" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P65" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="66">
@@ -3764,13 +3764,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N66" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O66" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P66" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="67">
@@ -3814,13 +3814,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N67" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O67" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P67" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="68">
@@ -3864,13 +3864,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N68" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O68" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P68" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="69">
@@ -3914,13 +3914,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N69" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O69" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P69" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="70">
@@ -3964,13 +3964,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N70" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O70" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P70" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="71">
@@ -4014,13 +4014,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N71" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O71" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P71" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="72">
@@ -4064,13 +4064,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N72" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O72" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P72" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="73">
@@ -4114,13 +4114,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N73" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O73" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P73" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="74">
@@ -4164,13 +4164,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N74" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O74" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P74" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="75">
@@ -4214,13 +4214,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N75" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O75" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P75" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="76">
@@ -4264,13 +4264,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N76" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O76" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P76" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="77">
@@ -4314,13 +4314,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N77" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O77" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P77" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="78">
@@ -4364,13 +4364,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N78" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O78" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P78" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="79">
@@ -4414,13 +4414,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N79" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O79" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P79" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="80">
@@ -4464,13 +4464,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N80" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O80" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P80" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="81">
@@ -4514,13 +4514,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N81" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O81" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P81" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="82">
@@ -4564,13 +4564,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N82" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O82" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P82" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="83">
@@ -4614,13 +4614,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N83" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O83" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P83" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="84">
@@ -4664,13 +4664,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N84" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O84" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P84" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="85">
@@ -4714,13 +4714,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N85" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O85" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P85" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="86">
@@ -4764,13 +4764,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N86" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O86" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P86" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="87">
@@ -4814,13 +4814,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N87" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O87" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P87" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="88">
@@ -4864,13 +4864,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N88" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O88" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P88" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="89">
@@ -4914,13 +4914,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N89" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O89" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P89" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="90">
@@ -4964,13 +4964,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N90" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O90" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P90" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="91">
@@ -5014,13 +5014,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N91" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O91" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P91" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="92">
@@ -5064,13 +5064,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N92" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O92" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P92" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="93">
@@ -5114,13 +5114,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N93" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O93" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P93" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="94">
@@ -5164,13 +5164,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N94" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O94" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P94" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="95">
@@ -5214,13 +5214,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N95" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O95" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P95" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="96">
@@ -5264,13 +5264,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N96" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O96" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P96" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="97">
@@ -5314,13 +5314,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N97" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O97" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P97" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="98">
@@ -5364,13 +5364,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N98" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O98" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P98" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="99">
@@ -5414,13 +5414,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N99" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O99" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P99" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="100">
@@ -5464,13 +5464,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N100" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O100" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P100" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="101">
@@ -5514,13 +5514,13 @@
         <v>Playwright Automation</v>
       </c>
       <c r="N101" t="str">
-        <v>01 Jul 2026</v>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O101" t="str">
         <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
       </c>
       <c r="P101" t="str">
-        <v/>
+        <v>Regression run — 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
   </sheetData>
@@ -5532,7 +5532,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P42"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5845,7 +5845,7 @@
         <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
       </c>
       <c r="K6" t="str">
-        <v>New</v>
+        <v>Fixed</v>
       </c>
       <c r="L6" t="str">
         <v>Playwright Automation</v>
@@ -5854,13 +5854,13 @@
         <v>01 Jul 2026</v>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O6" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>Fixed — verified in Playwright regression 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="7" xml:space="preserve">
@@ -5949,7 +5949,7 @@
         <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
       </c>
       <c r="K8" t="str">
-        <v>New</v>
+        <v>Fixed</v>
       </c>
       <c r="L8" t="str">
         <v>Playwright Automation</v>
@@ -5958,13 +5958,13 @@
         <v>01 Jul 2026</v>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O8" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>Fixed — verified in Playwright regression 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="9" xml:space="preserve">
@@ -6001,7 +6001,7 @@
         <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
       </c>
       <c r="K9" t="str">
-        <v>New</v>
+        <v>Fixed</v>
       </c>
       <c r="L9" t="str">
         <v>Playwright Automation</v>
@@ -6010,13 +6010,13 @@
         <v>01 Jul 2026</v>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O9" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="P9" t="str">
-        <v/>
+        <v>Fixed — verified in Playwright regression 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="10" xml:space="preserve">
@@ -6053,7 +6053,7 @@
         <v>Error: expect(received).toBe(expected) // Object.is equality Expected: true Received: false</v>
       </c>
       <c r="K10" t="str">
-        <v>New</v>
+        <v>Fixed</v>
       </c>
       <c r="L10" t="str">
         <v>Playwright Automation</v>
@@ -6062,13 +6062,13 @@
         <v>01 Jul 2026</v>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>02 Jul 2026</v>
       </c>
       <c r="O10" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>Fixed — verified in Playwright regression 7/2/2026, 7:49:55 PM</v>
       </c>
     </row>
     <row r="11" xml:space="preserve">
@@ -6695,9 +6695,1049 @@
         <v/>
       </c>
     </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>BUG-ADDNEWUSER-023</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Stat cards display all 4 metrics</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D23" t="str">
+        <v>TC-AQ-002</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F23" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G23" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H23" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-002
+3. Observe failure</v>
+      </c>
+      <c r="I23" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J23" t="str">
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
+      </c>
+      <c r="K23" t="str">
+        <v>New</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M23" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>BUG-ADDNEWUSER-024</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Grid displays all 10 expected column headers</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D24" t="str">
+        <v>TC-AQ-003</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F24" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G24" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H24" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-003
+3. Observe failure</v>
+      </c>
+      <c r="I24" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J24" t="str">
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
+      </c>
+      <c r="K24" t="str">
+        <v>New</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M24" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>BUG-ADDNEWUSER-026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>No-match search shows empty grid</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D25" t="str">
+        <v>TC-AQ-020</v>
+      </c>
+      <c r="E25" t="str">
+        <v>High</v>
+      </c>
+      <c r="F25" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G25" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H25" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-020
+3. Observe failure</v>
+      </c>
+      <c r="I25" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J25" t="str">
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
+      </c>
+      <c r="K25" t="str">
+        <v>New</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M25" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>BUG-ADDNEWUSER-027</v>
+      </c>
+      <c r="B26" t="str">
+        <v>EXPORT button is visible and clickable</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D26" t="str">
+        <v>TC-AQ-014</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F26" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G26" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H26" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-014
+3. Observe failure</v>
+      </c>
+      <c r="I26" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J26" t="str">
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
+      </c>
+      <c r="K26" t="str">
+        <v>New</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M26" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>BUG-ADDNEWUSER-028</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Pagination shows correct format</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D27" t="str">
+        <v>TC-AQ-015</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F27" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G27" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H27" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-015
+3. Observe failure</v>
+      </c>
+      <c r="I27" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J27" t="str">
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
+      </c>
+      <c r="K27" t="str">
+        <v>New</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M27" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>BUG-ADDNEWUSER-029</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Perform Action opens ActionQueueDetails page</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D28" t="str">
+        <v>TC-AQ-004</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F28" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G28" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H28" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-004
+3. Observe failure</v>
+      </c>
+      <c r="I28" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J28" t="str">
+        <v>TypeError: aq.navigateToActionQueue is not a function</v>
+      </c>
+      <c r="K28" t="str">
+        <v>New</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M28" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>BUG-ADDNEWUSER-030</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Detail page displays all 5 information sections</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D29" t="str">
+        <v>TC-AQ-005</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F29" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G29" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H29" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-005
+3. Observe failure</v>
+      </c>
+      <c r="I29" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J29" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K29" t="str">
+        <v>New</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M29" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>BUG-ADDNEWUSER-031</v>
+      </c>
+      <c r="B30" t="str">
+        <v>TIMELINE button opens timeline view</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D30" t="str">
+        <v>TC-AQ-026</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F30" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G30" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H30" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-026
+3. Observe failure</v>
+      </c>
+      <c r="I30" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J30" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K30" t="str">
+        <v>New</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M30" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
+        <v>BUG-ADDNEWUSER-032</v>
+      </c>
+      <c r="B31" t="str">
+        <v>APPROVE dialog opens with correct elements</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D31" t="str">
+        <v>TC-AQ-006</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F31" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G31" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H31" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-006
+3. Observe failure</v>
+      </c>
+      <c r="I31" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J31" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K31" t="str">
+        <v>New</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M31" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
+        <v>BUG-ADDNEWUSER-033</v>
+      </c>
+      <c r="B32" t="str">
+        <v>APPROVE with valid remarks submits successfully</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D32" t="str">
+        <v>TC-AQ-007</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F32" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G32" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H32" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-007
+3. Observe failure</v>
+      </c>
+      <c r="I32" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J32" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K32" t="str">
+        <v>New</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M32" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>BUG-ADDNEWUSER-034</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Cancel APPROVE dismisses without submitting</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D33" t="str">
+        <v>TC-AQ-010</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F33" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G33" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H33" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-010
+3. Observe failure</v>
+      </c>
+      <c r="I33" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J33" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K33" t="str">
+        <v>New</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M33" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>BUG-ADDNEWUSER-035</v>
+      </c>
+      <c r="B34" t="str">
+        <v>APPROVE empty remarks shows validation error</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D34" t="str">
+        <v>TC-AQ-016</v>
+      </c>
+      <c r="E34" t="str">
+        <v>High</v>
+      </c>
+      <c r="F34" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G34" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H34" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-016
+3. Observe failure</v>
+      </c>
+      <c r="I34" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J34" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K34" t="str">
+        <v>New</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M34" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>BUG-ADDNEWUSER-037</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Max length remarks (1000 chars) handled</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D35" t="str">
+        <v>TC-AQ-022</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F35" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G35" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H35" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-022
+3. Observe failure</v>
+      </c>
+      <c r="I35" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J35" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K35" t="str">
+        <v>New</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M35" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
+        <v>BUG-ADDNEWUSER-038</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Whitespace-only remarks rejected</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D36" t="str">
+        <v>TC-AQ-023</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F36" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G36" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H36" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-023
+3. Observe failure</v>
+      </c>
+      <c r="I36" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J36" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K36" t="str">
+        <v>New</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M36" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>BUG-ADDNEWUSER-039</v>
+      </c>
+      <c r="B37" t="str">
+        <v>SQL injection in remarks is sanitized</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D37" t="str">
+        <v>TC-AQ-024</v>
+      </c>
+      <c r="E37" t="str">
+        <v>High</v>
+      </c>
+      <c r="F37" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G37" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H37" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-024
+3. Observe failure</v>
+      </c>
+      <c r="I37" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J37" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K37" t="str">
+        <v>New</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M37" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
+        <v>BUG-ADDNEWUSER-040</v>
+      </c>
+      <c r="B38" t="str">
+        <v>XSS payload in remarks @security</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D38" t="str">
+        <v>TC-AQ-025</v>
+      </c>
+      <c r="E38" t="str">
+        <v>High</v>
+      </c>
+      <c r="F38" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G38" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H38" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-025
+3. Observe failure</v>
+      </c>
+      <c r="I38" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J38" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K38" t="str">
+        <v>New</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M38" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
+        <v>BUG-ADDNEWUSER-041</v>
+      </c>
+      <c r="B39" t="str">
+        <v>REOPEN dialog opens with correct elements</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D39" t="str">
+        <v>TC-AQ-008</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F39" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G39" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H39" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-008
+3. Observe failure</v>
+      </c>
+      <c r="I39" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J39" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K39" t="str">
+        <v>New</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M39" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
+        <v>BUG-ADDNEWUSER-042</v>
+      </c>
+      <c r="B40" t="str">
+        <v>REOPEN with valid remarks submits successfully</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D40" t="str">
+        <v>TC-AQ-009</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F40" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G40" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H40" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-009
+3. Observe failure</v>
+      </c>
+      <c r="I40" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J40" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K40" t="str">
+        <v>New</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M40" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
+        <v>BUG-ADDNEWUSER-043</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Cancel REOPEN dismisses without submitting</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D41" t="str">
+        <v>TC-AQ-011</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F41" t="str">
+        <v>P3</v>
+      </c>
+      <c r="G41" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H41" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-011
+3. Observe failure</v>
+      </c>
+      <c r="I41" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J41" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K41" t="str">
+        <v>New</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M41" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
+        <v>BUG-ADDNEWUSER-044</v>
+      </c>
+      <c r="B42" t="str">
+        <v>REOPEN empty remarks shows validation error</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Addnewuser</v>
+      </c>
+      <c r="D42" t="str">
+        <v>TC-AQ-017</v>
+      </c>
+      <c r="E42" t="str">
+        <v>High</v>
+      </c>
+      <c r="F42" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G42" t="str">
+        <v>http://customerportal.dev-ts.online | Chrome | Windows | Headless</v>
+      </c>
+      <c r="H42" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to Addnewuser feature
+2. Execute: TC-AQ-017
+3. Observe failure</v>
+      </c>
+      <c r="I42" t="str">
+        <v>All Playwright assertions should pass</v>
+      </c>
+      <c r="J42" t="str">
+        <v>TypeError: aq.navigateToActionQueueDetails is not a function</v>
+      </c>
+      <c r="K42" t="str">
+        <v>New</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Playwright Automation</v>
+      </c>
+      <c r="M42" t="str">
+        <v>02 Jul 2026</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P42"/>
   </ignoredErrors>
 </worksheet>
 </file>